--- a/outputs/data_audit.xlsx
+++ b/outputs/data_audit.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:E26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,12 +509,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>source_sheet</t>
+          <t>Land use type</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>str</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -524,18 +524,18 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Vegetation cover type</t>
+          <t>source_sheet</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>str</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -545,13 +545,13 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>soil type</t>
+          <t>Vegetation cover type</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -566,18 +566,18 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>soil type</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -587,18 +587,18 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>353</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>pH</t>
+          <t>geology</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -608,13 +608,13 @@
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>453</v>
+        <v>33</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SOM</t>
+          <t>K</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -629,13 +629,13 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>671</v>
+        <v>357</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CEC</t>
+          <t>pH</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -650,13 +650,13 @@
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>673</v>
+        <v>459</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>sand content</t>
+          <t>CEC</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -671,13 +671,13 @@
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>848</v>
+        <v>676</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Particle content</t>
+          <t>SOM</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -692,13 +692,13 @@
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>1089</v>
+        <v>679</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>clay content</t>
+          <t>sand content</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -713,13 +713,13 @@
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>1273</v>
+        <v>864</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>altitude</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -734,13 +734,13 @@
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>1543</v>
+        <v>896</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Mn</t>
+          <t>Particle content</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -755,18 +755,18 @@
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>1750</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>clay content</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -776,18 +776,18 @@
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>1983</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>water content</t>
+          <t>P</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -797,13 +797,13 @@
         <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>2462</v>
+        <v>1590</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>BCF</t>
+          <t>Mn</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -818,18 +818,18 @@
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>4117</v>
+        <v>1813</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>N</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -839,13 +839,13 @@
         <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>4632</v>
+        <v>2057</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>water content</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -860,13 +860,13 @@
         <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>4646</v>
+        <v>2555</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>bulk density</t>
+          <t>BCF</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -881,28 +881,91 @@
         <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>4647</v>
+        <v>4473</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>float64</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" t="n">
+        <v>5010</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>float64</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" t="n">
+        <v>5024</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>bulk density</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>float64</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" t="n">
+        <v>5028</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
           <t>Distance from pollution source</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>float64</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" t="n">
-        <v>4661</v>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>float64</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" t="n">
+        <v>5043</v>
       </c>
     </row>
   </sheetData>
